--- a/analysis/econometrics_outputs/sdid/Graficos/contracts/sdid_levels_cosine_weighted_top_vs_bottom.xlsx
+++ b/analysis/econometrics_outputs/sdid/Graficos/contracts/sdid_levels_cosine_weighted_top_vs_bottom.xlsx
@@ -507,13 +507,13 @@
         <v>2711.13679245283</v>
       </c>
       <c r="I2" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J2" t="n">
-        <v>-912.6439033572933</v>
+        <v>-941.5024746104743</v>
       </c>
       <c r="K2" t="n">
-        <v>258.6271656823083</v>
+        <v>287.4857369354893</v>
       </c>
     </row>
     <row r="3">
@@ -550,13 +550,13 @@
         <v>2419.627358490566</v>
       </c>
       <c r="I3" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J3" t="n">
-        <v>-690.8844693950291</v>
+        <v>-719.7430406482101</v>
       </c>
       <c r="K3" t="n">
-        <v>480.3865996445725</v>
+        <v>509.2451708977535</v>
       </c>
     </row>
     <row r="4">
@@ -593,13 +593,13 @@
         <v>2738.77358490566</v>
       </c>
       <c r="I4" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J4" t="n">
-        <v>-699.3532764552845</v>
+        <v>-728.2118477084655</v>
       </c>
       <c r="K4" t="n">
-        <v>471.9177925843171</v>
+        <v>500.7763638374981</v>
       </c>
     </row>
     <row r="5">
@@ -636,13 +636,13 @@
         <v>2659.037735849056</v>
       </c>
       <c r="I5" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J5" t="n">
-        <v>-657.3432338502939</v>
+        <v>-686.201805103475</v>
       </c>
       <c r="K5" t="n">
-        <v>513.9278351893076</v>
+        <v>542.7864064424887</v>
       </c>
     </row>
     <row r="6">
@@ -679,13 +679,13 @@
         <v>2798.004716981132</v>
       </c>
       <c r="I6" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J6" t="n">
-        <v>-689.3263440146279</v>
+        <v>-718.1849152678089</v>
       </c>
       <c r="K6" t="n">
-        <v>481.9447250249736</v>
+        <v>510.8032962781547</v>
       </c>
     </row>
     <row r="7">
@@ -722,13 +722,13 @@
         <v>3268.117924528302</v>
       </c>
       <c r="I7" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J7" t="n">
-        <v>-720.4718096263136</v>
+        <v>-749.3303808794947</v>
       </c>
       <c r="K7" t="n">
-        <v>450.7992594132879</v>
+        <v>479.657830666469</v>
       </c>
     </row>
     <row r="8">
@@ -765,13 +765,13 @@
         <v>3486.396226415094</v>
       </c>
       <c r="I8" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J8" t="n">
-        <v>-1003.266240545363</v>
+        <v>-1032.124811798544</v>
       </c>
       <c r="K8" t="n">
-        <v>168.0048284942382</v>
+        <v>196.8633997474192</v>
       </c>
     </row>
     <row r="9">
@@ -808,13 +808,13 @@
         <v>2852.462264150944</v>
       </c>
       <c r="I9" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J9" t="n">
-        <v>-1056.041955700568</v>
+        <v>-1084.900526953749</v>
       </c>
       <c r="K9" t="n">
-        <v>115.2291133390333</v>
+        <v>144.0876845922144</v>
       </c>
     </row>
     <row r="10">
@@ -851,13 +851,13 @@
         <v>3453.990566037735</v>
       </c>
       <c r="I10" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J10" t="n">
-        <v>-878.5541285551021</v>
+        <v>-907.4126998082832</v>
       </c>
       <c r="K10" t="n">
-        <v>292.7169404844994</v>
+        <v>321.5755117376805</v>
       </c>
     </row>
     <row r="11">
@@ -894,13 +894,13 @@
         <v>3341.033018867925</v>
       </c>
       <c r="I11" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J11" t="n">
-        <v>-789.7094846110977</v>
+        <v>-818.5680558642787</v>
       </c>
       <c r="K11" t="n">
-        <v>381.5615844285039</v>
+        <v>410.4201556816849</v>
       </c>
     </row>
     <row r="12">
@@ -937,13 +937,13 @@
         <v>3736</v>
       </c>
       <c r="I12" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J12" t="n">
-        <v>-1041.184530259301</v>
+        <v>-1070.043101512483</v>
       </c>
       <c r="K12" t="n">
-        <v>130.0865387803001</v>
+        <v>158.9451100334811</v>
       </c>
     </row>
     <row r="13">
@@ -980,13 +980,13 @@
         <v>3063.141509433962</v>
       </c>
       <c r="I13" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J13" t="n">
-        <v>-803.6324913061671</v>
+        <v>-832.4910625593482</v>
       </c>
       <c r="K13" t="n">
-        <v>367.6385777334344</v>
+        <v>396.4971489866155</v>
       </c>
     </row>
     <row r="14">
@@ -1023,13 +1023,13 @@
         <v>3085.811320754717</v>
       </c>
       <c r="I14" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J14" t="n">
-        <v>-867.0684316591801</v>
+        <v>-895.9270029123611</v>
       </c>
       <c r="K14" t="n">
-        <v>304.2026373804215</v>
+        <v>333.0612086336025</v>
       </c>
     </row>
     <row r="15">
@@ -1066,13 +1066,13 @@
         <v>2599.768867924528</v>
       </c>
       <c r="I15" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J15" t="n">
-        <v>-430.2759788289918</v>
+        <v>-459.1345500821728</v>
       </c>
       <c r="K15" t="n">
-        <v>740.9950902106098</v>
+        <v>769.8536614637908</v>
       </c>
     </row>
     <row r="16">
@@ -1109,13 +1109,13 @@
         <v>2861.844339622641</v>
       </c>
       <c r="I16" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J16" t="n">
-        <v>-266.9643537529109</v>
+        <v>-295.822925006092</v>
       </c>
       <c r="K16" t="n">
-        <v>904.3067152866906</v>
+        <v>933.1652865398717</v>
       </c>
     </row>
     <row r="17">
@@ -1152,13 +1152,13 @@
         <v>2620.915094339623</v>
       </c>
       <c r="I17" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J17" t="n">
-        <v>-398.8980116956989</v>
+        <v>-427.7565829488799</v>
       </c>
       <c r="K17" t="n">
-        <v>772.3730573439027</v>
+        <v>801.2316285970837</v>
       </c>
     </row>
     <row r="18">
@@ -1195,13 +1195,13 @@
         <v>2855.278301886793</v>
       </c>
       <c r="I18" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J18" t="n">
-        <v>-468.1402515009336</v>
+        <v>-496.9988227541146</v>
       </c>
       <c r="K18" t="n">
-        <v>703.130817538668</v>
+        <v>731.989388791849</v>
       </c>
     </row>
     <row r="19">
@@ -1238,13 +1238,13 @@
         <v>3122.665094339623</v>
       </c>
       <c r="I19" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J19" t="n">
-        <v>-466.5109149215064</v>
+        <v>-495.3694861746874</v>
       </c>
       <c r="K19" t="n">
-        <v>704.7601541180952</v>
+        <v>733.6187253712762</v>
       </c>
     </row>
     <row r="20">
@@ -1281,13 +1281,13 @@
         <v>3027.099056603774</v>
       </c>
       <c r="I20" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J20" t="n">
-        <v>-516.0093933146891</v>
+        <v>-544.8679645678701</v>
       </c>
       <c r="K20" t="n">
-        <v>655.2616757249125</v>
+        <v>684.1202469780935</v>
       </c>
     </row>
     <row r="21">
@@ -1324,13 +1324,13 @@
         <v>2454.52358490566</v>
       </c>
       <c r="I21" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J21" t="n">
-        <v>-585.6355345198008</v>
+        <v>-614.4941057729818</v>
       </c>
       <c r="K21" t="n">
-        <v>585.6355345198008</v>
+        <v>614.4941057729818</v>
       </c>
     </row>
     <row r="22">
@@ -1367,13 +1367,13 @@
         <v>2818.042452830189</v>
       </c>
       <c r="I22" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J22" t="n">
-        <v>-273.751176637878</v>
+        <v>-302.609747891059</v>
       </c>
       <c r="K22" t="n">
-        <v>897.5198924017236</v>
+        <v>926.3784636549046</v>
       </c>
     </row>
     <row r="23">
@@ -1410,13 +1410,13 @@
         <v>2618.509433962264</v>
       </c>
       <c r="I23" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J23" t="n">
-        <v>-209.9520287376949</v>
+        <v>-238.810599990876</v>
       </c>
       <c r="K23" t="n">
-        <v>961.3190403019066</v>
+        <v>990.1776115550877</v>
       </c>
     </row>
     <row r="24">
@@ -1453,13 +1453,13 @@
         <v>2523.301886792452</v>
       </c>
       <c r="I24" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J24" t="n">
-        <v>-219.0751267291739</v>
+        <v>-247.9336979823549</v>
       </c>
       <c r="K24" t="n">
-        <v>952.1959423104277</v>
+        <v>981.0545135636087</v>
       </c>
     </row>
     <row r="25">
@@ -1496,13 +1496,13 @@
         <v>2064.325471698113</v>
       </c>
       <c r="I25" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J25" t="n">
-        <v>-199.6632277638664</v>
+        <v>-228.5217990170474</v>
       </c>
       <c r="K25" t="n">
-        <v>971.6078412757352</v>
+        <v>1000.466412528916</v>
       </c>
     </row>
     <row r="26">
@@ -1539,13 +1539,13 @@
         <v>2167.622641509434</v>
       </c>
       <c r="I26" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J26" t="n">
-        <v>-275.4039459622848</v>
+        <v>-304.2625172154658</v>
       </c>
       <c r="K26" t="n">
-        <v>895.8671230773168</v>
+        <v>924.7256943304978</v>
       </c>
     </row>
     <row r="27">
@@ -1582,13 +1582,13 @@
         <v>1904.731132075471</v>
       </c>
       <c r="I27" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J27" t="n">
-        <v>-75.99630749606376</v>
+        <v>-104.8548787492448</v>
       </c>
       <c r="K27" t="n">
-        <v>1095.274761543538</v>
+        <v>1124.133332796719</v>
       </c>
     </row>
     <row r="28">
@@ -1625,13 +1625,13 @@
         <v>2338.066037735849</v>
       </c>
       <c r="I28" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J28" t="n">
-        <v>-260.2183099306351</v>
+        <v>-289.0768811838161</v>
       </c>
       <c r="K28" t="n">
-        <v>911.0527591089665</v>
+        <v>939.9113303621475</v>
       </c>
     </row>
     <row r="29">
@@ -1668,13 +1668,13 @@
         <v>1989.075471698113</v>
       </c>
       <c r="I29" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J29" t="n">
-        <v>-175.0019374412864</v>
+        <v>-203.8605086944674</v>
       </c>
       <c r="K29" t="n">
-        <v>996.2691315983152</v>
+        <v>1025.127702851496</v>
       </c>
     </row>
     <row r="30">
@@ -1711,13 +1711,13 @@
         <v>2376.551886792452</v>
       </c>
       <c r="I30" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J30" t="n">
-        <v>-279.1719009227224</v>
+        <v>-308.0304721759035</v>
       </c>
       <c r="K30" t="n">
-        <v>892.0991681168791</v>
+        <v>920.9577393700602</v>
       </c>
     </row>
     <row r="31">
@@ -1754,13 +1754,13 @@
         <v>2582.896226415094</v>
       </c>
       <c r="I31" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J31" t="n">
-        <v>-226.2097889324609</v>
+        <v>-255.068360185642</v>
       </c>
       <c r="K31" t="n">
-        <v>945.0612801071406</v>
+        <v>973.9198513603217</v>
       </c>
     </row>
     <row r="32">
@@ -1797,13 +1797,13 @@
         <v>2554.811320754717</v>
       </c>
       <c r="I32" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J32" t="n">
-        <v>-301.7458510140189</v>
+        <v>-330.6044222671999</v>
       </c>
       <c r="K32" t="n">
-        <v>869.5252180255827</v>
+        <v>898.3837892787637</v>
       </c>
     </row>
     <row r="33">
@@ -1840,13 +1840,13 @@
         <v>2080.533018867924</v>
       </c>
       <c r="I33" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J33" t="n">
-        <v>-473.7014200949682</v>
+        <v>-502.5599913481492</v>
       </c>
       <c r="K33" t="n">
-        <v>697.5696489446334</v>
+        <v>726.4282201978144</v>
       </c>
     </row>
     <row r="34">
@@ -1883,13 +1883,13 @@
         <v>2389.122641509433</v>
       </c>
       <c r="I34" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J34" t="n">
-        <v>-225.1297524138968</v>
+        <v>-253.9883236670778</v>
       </c>
       <c r="K34" t="n">
-        <v>946.1413166257048</v>
+        <v>974.9998878788858</v>
       </c>
     </row>
     <row r="35">
@@ -1926,13 +1926,13 @@
         <v>2399.528301886792</v>
       </c>
       <c r="I35" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J35" t="n">
-        <v>-158.8821869848041</v>
+        <v>-187.7407582379851</v>
       </c>
       <c r="K35" t="n">
-        <v>1012.388882054797</v>
+        <v>1041.247453307979</v>
       </c>
     </row>
     <row r="36">
@@ -1969,13 +1969,13 @@
         <v>2316.693396226415</v>
       </c>
       <c r="I36" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J36" t="n">
-        <v>-19.66018455023345</v>
+        <v>-48.51875580341448</v>
       </c>
       <c r="K36" t="n">
-        <v>1151.610884489368</v>
+        <v>1180.469455742549</v>
       </c>
     </row>
     <row r="37">
@@ -2012,13 +2012,13 @@
         <v>1928.165094339622</v>
       </c>
       <c r="I37" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J37" t="n">
-        <v>-177.0996245989245</v>
+        <v>-205.9581958521055</v>
       </c>
       <c r="K37" t="n">
-        <v>994.1714444406771</v>
+        <v>1023.030015693858</v>
       </c>
     </row>
     <row r="38">
@@ -2055,13 +2055,13 @@
         <v>2210.429245283019</v>
       </c>
       <c r="I38" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J38" t="n">
-        <v>-302.8637755423208</v>
+        <v>-331.7223467955018</v>
       </c>
       <c r="K38" t="n">
-        <v>868.4072934972808</v>
+        <v>897.2658647504618</v>
       </c>
     </row>
     <row r="39">
@@ -2098,13 +2098,13 @@
         <v>2021.037735849056</v>
       </c>
       <c r="I39" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J39" t="n">
-        <v>-147.8190403019069</v>
+        <v>-176.6776115550879</v>
       </c>
       <c r="K39" t="n">
-        <v>1023.452028737695</v>
+        <v>1052.310599990876</v>
       </c>
     </row>
     <row r="40">
@@ -2141,13 +2141,13 @@
         <v>1954.193396226415</v>
       </c>
       <c r="I40" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J40" t="n">
-        <v>-96.2408297115237</v>
+        <v>-125.0994009647047</v>
       </c>
       <c r="K40" t="n">
-        <v>1075.030239328078</v>
+        <v>1103.888810581259</v>
       </c>
     </row>
     <row r="41">
@@ -2184,13 +2184,13 @@
         <v>2184.867924528302</v>
       </c>
       <c r="I41" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J41" t="n">
-        <v>-180.6330999488944</v>
+        <v>-209.4916712020754</v>
       </c>
       <c r="K41" t="n">
-        <v>990.6379690907072</v>
+        <v>1019.496540343888</v>
       </c>
     </row>
     <row r="42">
@@ -2227,13 +2227,13 @@
         <v>2269.801886792453</v>
       </c>
       <c r="I42" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J42" t="n">
-        <v>-239.4783525356261</v>
+        <v>-268.3369237888071</v>
       </c>
       <c r="K42" t="n">
-        <v>931.7927165039755</v>
+        <v>960.6512877571565</v>
       </c>
     </row>
     <row r="43">
@@ -2270,13 +2270,13 @@
         <v>2416.264150943396</v>
       </c>
       <c r="I43" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J43" t="n">
-        <v>-165.4890037833434</v>
+        <v>-194.3475750365244</v>
       </c>
       <c r="K43" t="n">
-        <v>1005.782065256258</v>
+        <v>1034.640636509439</v>
       </c>
     </row>
     <row r="44">
@@ -2313,13 +2313,13 @@
         <v>2747.603773584905</v>
       </c>
       <c r="I44" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J44" t="n">
-        <v>-350.6431425538844</v>
+        <v>-379.5017138070655</v>
       </c>
       <c r="K44" t="n">
-        <v>820.6279264857171</v>
+        <v>849.4864977388982</v>
       </c>
     </row>
     <row r="45">
@@ -2356,13 +2356,13 @@
         <v>1981.77358490566</v>
       </c>
       <c r="I45" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J45" t="n">
-        <v>-396.0548893585108</v>
+        <v>-424.9134606116918</v>
       </c>
       <c r="K45" t="n">
-        <v>775.2161796810908</v>
+        <v>804.0747509342718</v>
       </c>
     </row>
     <row r="46">
@@ -2399,13 +2399,13 @@
         <v>2438.816037735849</v>
       </c>
       <c r="I46" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J46" t="n">
-        <v>-226.2102454145056</v>
+        <v>-255.0688166676866</v>
       </c>
       <c r="K46" t="n">
-        <v>945.060823625096</v>
+        <v>973.919394878277</v>
       </c>
     </row>
     <row r="47">
@@ -2442,13 +2442,13 @@
         <v>2665.009433962264</v>
       </c>
       <c r="I47" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J47" t="n">
-        <v>-314.7423513183403</v>
+        <v>-343.6009225715213</v>
       </c>
       <c r="K47" t="n">
-        <v>856.5287177212613</v>
+        <v>885.3872889744423</v>
       </c>
     </row>
     <row r="48">
@@ -2485,13 +2485,13 @@
         <v>2297.207547169811</v>
       </c>
       <c r="I48" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J48" t="n">
-        <v>-244.5453032355649</v>
+        <v>-273.4038744887459</v>
       </c>
       <c r="K48" t="n">
-        <v>926.7257658040367</v>
+        <v>955.5843370572177</v>
       </c>
     </row>
     <row r="49">
@@ -2528,13 +2528,13 @@
         <v>2030.721698113208</v>
       </c>
       <c r="I49" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J49" t="n">
-        <v>-204.422357404768</v>
+        <v>-233.2809286579491</v>
       </c>
       <c r="K49" t="n">
-        <v>966.8487116348335</v>
+        <v>995.7072828880146</v>
       </c>
     </row>
     <row r="50">
@@ -2571,13 +2571,13 @@
         <v>2226.193396226415</v>
       </c>
       <c r="I50" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J50" t="n">
-        <v>-327.6037329373298</v>
+        <v>-356.4623041905108</v>
       </c>
       <c r="K50" t="n">
-        <v>843.6673361022717</v>
+        <v>872.5259073554528</v>
       </c>
     </row>
     <row r="51">
@@ -2614,13 +2614,13 @@
         <v>1966.688679245283</v>
       </c>
       <c r="I51" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J51" t="n">
-        <v>-171.5667578916818</v>
+        <v>-200.4253291448629</v>
       </c>
       <c r="K51" t="n">
-        <v>999.7043111479197</v>
+        <v>1028.562882401101</v>
       </c>
     </row>
     <row r="52">
@@ -2657,13 +2657,13 @@
         <v>2116.632075471698</v>
       </c>
       <c r="I52" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J52" t="n">
-        <v>-185.260154118097</v>
+        <v>-214.1187253712781</v>
       </c>
       <c r="K52" t="n">
-        <v>986.0109149215045</v>
+        <v>1014.869486174686</v>
       </c>
     </row>
     <row r="53">
@@ -2700,13 +2700,13 @@
         <v>2003.52358490566</v>
       </c>
       <c r="I53" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J53" t="n">
-        <v>-163.2484377456076</v>
+        <v>-192.1070089987886</v>
       </c>
       <c r="K53" t="n">
-        <v>1008.022631293994</v>
+        <v>1036.881202547175</v>
       </c>
     </row>
     <row r="54">
@@ -2743,13 +2743,13 @@
         <v>2309.650943396226</v>
       </c>
       <c r="I54" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J54" t="n">
-        <v>-294.0693446232706</v>
+        <v>-322.9279158764516</v>
       </c>
       <c r="K54" t="n">
-        <v>877.201724416331</v>
+        <v>906.060295669512</v>
       </c>
     </row>
     <row r="55">
@@ -2786,13 +2786,13 @@
         <v>2640.556603773585</v>
       </c>
       <c r="I55" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J55" t="n">
-        <v>-280.9185533877262</v>
+        <v>-309.7771246409072</v>
       </c>
       <c r="K55" t="n">
-        <v>890.3525156518754</v>
+        <v>919.2110869050564</v>
       </c>
     </row>
     <row r="56">
@@ -2829,13 +2829,13 @@
         <v>3000.971698113208</v>
       </c>
       <c r="I56" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J56" t="n">
-        <v>-578.3094541789615</v>
+        <v>-607.1680254321425</v>
       </c>
       <c r="K56" t="n">
-        <v>592.9616148606401</v>
+        <v>621.8201861138211</v>
       </c>
     </row>
     <row r="57">
@@ -2872,13 +2872,13 @@
         <v>2042.193396226415</v>
       </c>
       <c r="I57" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J57" t="n">
-        <v>-465.5472813244266</v>
+        <v>-494.4058525776077</v>
       </c>
       <c r="K57" t="n">
-        <v>705.7237877151749</v>
+        <v>734.5823589683559</v>
       </c>
     </row>
     <row r="58">
@@ -2915,13 +2915,13 @@
         <v>2691.632075471698</v>
       </c>
       <c r="I58" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J58" t="n">
-        <v>-316.7682186342258</v>
+        <v>-345.6267898874069</v>
       </c>
       <c r="K58" t="n">
-        <v>854.5028504053757</v>
+        <v>883.3614216585568</v>
       </c>
     </row>
     <row r="59">
@@ -2958,13 +2958,13 @@
         <v>2644.966981132075</v>
       </c>
       <c r="I59" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J59" t="n">
-        <v>-308.9821565526681</v>
+        <v>-337.8407278058492</v>
       </c>
       <c r="K59" t="n">
-        <v>862.2889124869334</v>
+        <v>891.1474837401145</v>
       </c>
     </row>
     <row r="60">
@@ -3001,13 +3001,13 @@
         <v>2367.330188679245</v>
       </c>
       <c r="I60" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J60" t="n">
-        <v>-310.2324608740312</v>
+        <v>-339.0910321272122</v>
       </c>
       <c r="K60" t="n">
-        <v>861.0386081655704</v>
+        <v>889.8971794187514</v>
       </c>
     </row>
     <row r="61">
@@ -3044,13 +3044,13 @@
         <v>2200.457547169811</v>
       </c>
       <c r="I61" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J61" t="n">
-        <v>-316.6340129129844</v>
+        <v>-345.4925841661654</v>
       </c>
       <c r="K61" t="n">
-        <v>854.6370561266172</v>
+        <v>883.4956273797982</v>
       </c>
     </row>
     <row r="62">
@@ -3087,13 +3087,13 @@
         <v>2249.122641509434</v>
       </c>
       <c r="I62" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J62" t="n">
-        <v>-449.7345911235752</v>
+        <v>-478.5931623767563</v>
       </c>
       <c r="K62" t="n">
-        <v>721.5364779160263</v>
+        <v>750.3950491692074</v>
       </c>
     </row>
     <row r="63">
@@ -3130,13 +3130,13 @@
         <v>2071.358490566038</v>
       </c>
       <c r="I63" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J63" t="n">
-        <v>-284.4946337285662</v>
+        <v>-313.3532049817472</v>
       </c>
       <c r="K63" t="n">
-        <v>886.7764353110354</v>
+        <v>915.6350065642164</v>
       </c>
     </row>
     <row r="64">
@@ -3173,13 +3173,13 @@
         <v>2364.75</v>
       </c>
       <c r="I64" t="n">
-        <v>298.7936400611229</v>
+        <v>313.5174009045826</v>
       </c>
       <c r="J64" t="n">
-        <v>-339.7167883238183</v>
+        <v>-368.5753595769993</v>
       </c>
       <c r="K64" t="n">
-        <v>831.5542807157833</v>
+        <v>860.4128519689643</v>
       </c>
     </row>
   </sheetData>
